--- a/raw/hyphal length.xlsx
+++ b/raw/hyphal length.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10112"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/snekz/Desktop/mosaic/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/snekz/Desktop/Thesis/ABS_second_round/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6B68C88-F1B8-604E-8530-40E7702FBA75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F7D9B18-EB25-0F4E-BBCA-A7D6878AE880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14140" yWindow="760" windowWidth="16100" windowHeight="18880" activeTab="1" xr2:uid="{6E1B8530-874C-8D42-B1CD-D729819EB102}"/>
+    <workbookView xWindow="8260" yWindow="760" windowWidth="21980" windowHeight="18880" xr2:uid="{6E1B8530-874C-8D42-B1CD-D729819EB102}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -533,7 +533,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -543,6 +543,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -624,7 +630,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2721,7 +2727,7 @@
         <v>139</v>
       </c>
       <c r="B220">
-        <v>0.02</v>
+        <v>2E-3</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.2">
@@ -2729,7 +2735,7 @@
         <v>139</v>
       </c>
       <c r="B221">
-        <v>0.04</v>
+        <v>4.0000000000000001E-3</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.2">
@@ -2745,7 +2751,7 @@
         <v>139</v>
       </c>
       <c r="B223">
-        <v>0.04</v>
+        <v>4.0000000000000001E-3</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.2">
@@ -2753,7 +2759,7 @@
         <v>139</v>
       </c>
       <c r="B224">
-        <v>0.04</v>
+        <v>4.0000000000000001E-3</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.2">
@@ -2761,7 +2767,7 @@
         <v>139</v>
       </c>
       <c r="B225">
-        <v>0.02</v>
+        <v>2E-3</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.2">
@@ -2769,7 +2775,7 @@
         <v>139</v>
       </c>
       <c r="B226">
-        <v>0.04</v>
+        <v>4.0000000000000001E-3</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.2">
@@ -2777,7 +2783,7 @@
         <v>139</v>
       </c>
       <c r="B227">
-        <v>0.08</v>
+        <v>8.0000000000000002E-3</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.2">
@@ -11942,7 +11948,7 @@
       <c r="D9" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F9" s="3" t="s">
@@ -12022,7 +12028,7 @@
       <c r="D11" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F11" s="3" t="s">
@@ -12144,7 +12150,7 @@
       <c r="D14" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F14" s="3" t="s">
@@ -12266,7 +12272,7 @@
       <c r="D17" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F17" s="3" t="s">
@@ -12386,7 +12392,7 @@
       <c r="D20" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F20" s="3" t="s">
@@ -12874,7 +12880,7 @@
       <c r="D32" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="E32" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F32" s="3" t="s">
@@ -12914,7 +12920,7 @@
       <c r="D33" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="E33" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F33" s="3" t="s">
@@ -13115,7 +13121,7 @@
       <c r="D38" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="E38" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F38" s="3" t="s">
@@ -13232,7 +13238,7 @@
       <c r="D41" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E41" s="3" t="s">
+      <c r="E41" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F41" s="3" t="s">
@@ -13294,7 +13300,7 @@
       <c r="D43" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E43" s="3" t="s">
+      <c r="E43" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F43" s="3" t="s">
@@ -13334,7 +13340,7 @@
       <c r="D45" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="E45" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F45" s="3" t="s">
@@ -13377,7 +13383,7 @@
       <c r="D47" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="E47" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F47" s="3" t="s">
@@ -13457,7 +13463,7 @@
       <c r="D51" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E51" s="3" t="s">
+      <c r="E51" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F51" s="3" t="s">
@@ -13540,7 +13546,7 @@
       <c r="D55" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E55" s="3" t="s">
+      <c r="E55" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F55" s="8" t="s">
@@ -13603,7 +13609,7 @@
       <c r="D58" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E58" s="3" t="s">
+      <c r="E58" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F58" s="3" t="s">
@@ -13643,7 +13649,7 @@
       <c r="D60" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E60" s="3" t="s">
+      <c r="E60" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F60" s="8" t="s">
@@ -13686,7 +13692,7 @@
       <c r="D62" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E62" s="3" t="s">
+      <c r="E62" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F62" s="3" t="s">
@@ -13706,7 +13712,7 @@
       <c r="D63" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E63" s="3" t="s">
+      <c r="E63" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F63" s="3" t="s">
@@ -13746,7 +13752,7 @@
       <c r="D65" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E65" s="3" t="s">
+      <c r="E65" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F65" s="3" t="s">
@@ -13769,7 +13775,7 @@
       <c r="D66" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E66" s="3" t="s">
+      <c r="E66" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F66" s="3" t="s">
@@ -13809,7 +13815,7 @@
       <c r="D68" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E68" s="3" t="s">
+      <c r="E68" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F68" s="3" t="s">
@@ -13952,7 +13958,7 @@
       <c r="D75" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E75" s="3" t="s">
+      <c r="E75" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F75" s="3" t="s">
@@ -13972,7 +13978,7 @@
       <c r="D76" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E76" s="3" t="s">
+      <c r="E76" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F76" s="3" t="s">
@@ -14150,7 +14156,7 @@
       <c r="D84" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E84" s="3" t="s">
+      <c r="E84" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F84" s="3" t="s">
@@ -14273,7 +14279,7 @@
       <c r="D90" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E90" s="3" t="s">
+      <c r="E90" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F90" s="3" t="s">
@@ -14316,7 +14322,7 @@
       <c r="D92" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E92" s="3" t="s">
+      <c r="E92" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F92" s="3" t="s">
@@ -14379,7 +14385,7 @@
       <c r="D95" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E95" s="3" t="s">
+      <c r="E95" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F95" s="3" t="s">
@@ -14442,7 +14448,7 @@
       <c r="D98" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E98" s="3" t="s">
+      <c r="E98" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F98" s="3" t="s">
@@ -14462,7 +14468,7 @@
       <c r="D99" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E99" s="3" t="s">
+      <c r="E99" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F99" s="3" t="s">
@@ -14505,7 +14511,7 @@
       <c r="D101" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E101" s="3" t="s">
+      <c r="E101" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F101" s="3" t="s">
@@ -14588,7 +14594,7 @@
       <c r="D105" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E105" s="3" t="s">
+      <c r="E105" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F105" s="3" t="s">
@@ -14608,7 +14614,7 @@
       <c r="D106" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E106" s="3" t="s">
+      <c r="E106" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F106" s="3" t="s">
@@ -14754,7 +14760,7 @@
       <c r="D113" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E113" s="3" t="s">
+      <c r="E113" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F113" s="3" t="s">
@@ -14774,7 +14780,7 @@
       <c r="D114" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E114" s="3" t="s">
+      <c r="E114" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F114" s="3" t="s">
@@ -14814,7 +14820,7 @@
       <c r="D116" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E116" s="3" t="s">
+      <c r="E116" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F116" s="3" t="s">
@@ -14917,13 +14923,13 @@
       <c r="D121" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E121" s="3" t="s">
+      <c r="E121" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F121" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G121" s="9" t="s">
+      <c r="G121" s="3" t="s">
         <v>34</v>
       </c>
     </row>
